--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,30 +446,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -478,13 +478,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -503,7 +503,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,6 +516,25 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,7 +439,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Cumulative Total</t>
+          <t>Cumulative Steps</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Cumulative Points</t>
         </is>
       </c>
     </row>
@@ -459,17 +464,20 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
+        <v>105386</v>
+      </c>
+      <c r="F2" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -478,17 +486,20 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -497,17 +508,20 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -516,13 +530,16 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -535,6 +552,9 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -461,13 +461,13 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>105386</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>105386</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -489,17 +489,17 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -511,17 +511,17 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -533,17 +533,17 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -555,7 +555,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,29 +451,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>105386</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3390</v>
       </c>
       <c r="F2" t="n">
-        <v>105386</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -483,23 +483,23 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>105386</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -511,7 +511,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -533,17 +533,17 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -555,7 +555,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,20 +452,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
       <c r="E2" t="n">
-        <v>3390</v>
+        <v>105386</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
@@ -473,33 +474,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>105386</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -511,13 +512,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -556,6 +557,257 @@
       </c>
       <c r="F6" t="n">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Total Steps</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Total Distance (Jogging/Running (Km))</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Total Distance (Cycling (Km))</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Steps Points</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Run/Jog Points</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Cycling Points</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chee</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Surya</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>105386</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chun Chieh</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -452,7 +452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -462,23 +462,23 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>105386</v>
+        <v>3390</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -490,7 +490,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -534,17 +534,17 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>105386</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -645,7 +645,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>29.45</v>
+        <v>36.89</v>
       </c>
       <c r="D3" t="n">
         <v>4.78</v>
@@ -654,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -745,7 +745,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>17.97</v>
+        <v>22.99</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,7 +465,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3390</v>
+        <v>5279</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -518,7 +518,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>29156</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>29156</v>
       </c>
       <c r="C2" t="n">
         <v>8.210000000000001</v>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1889</v>
       </c>
       <c r="C3" t="n">
         <v>36.89</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>21.41</v>
+        <v>27.04</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -745,7 +745,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>22.99</v>
+        <v>30.56</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,11 +452,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -465,20 +465,20 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>5279</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -487,16 +487,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3390</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -509,7 +509,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>73394</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>29156</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -540,22 +540,62 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>60056</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Surya</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>105386</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -617,10 +657,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29156</v>
+        <v>73394</v>
       </c>
       <c r="C2" t="n">
-        <v>8.210000000000001</v>
+        <v>4.14</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -642,19 +682,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1889</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>36.89</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -670,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>27.04</v>
+        <v>39.38</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -745,7 +785,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>30.56</v>
+        <v>58.94</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -754,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -767,7 +807,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>60056</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>105386</v>
+        <v>115111</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -596,6 +596,28 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chee</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>29381</v>
+      </c>
+      <c r="F9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -732,7 +754,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>29381</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -757,7 +779,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105386</v>
+        <v>115111</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,11 +450,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
         <v>0</v>
       </c>
@@ -465,7 +461,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>5279</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -474,7 +470,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,7 +483,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3390</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -496,7 +492,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kai Fong</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -518,7 +514,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -531,7 +527,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>29156</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -540,22 +536,88 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>CRX</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>73394</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Surya</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>105386</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>157328</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>60056</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chee</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>69621</v>
+      </c>
+      <c r="F9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -617,10 +679,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29156</v>
+        <v>73394</v>
       </c>
       <c r="C2" t="n">
-        <v>8.210000000000001</v>
+        <v>7.66</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -642,13 +704,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1889</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>36.89</v>
+        <v>73.69</v>
       </c>
       <c r="D3" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -670,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>27.04</v>
+        <v>39.38</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -692,7 +754,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>69621</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -717,7 +779,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105386</v>
+        <v>157328</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -745,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>30.56</v>
+        <v>58.94</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -767,7 +829,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>60056</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -450,9 +450,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -464,7 +468,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -474,7 +478,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -486,17 +490,17 @@
         <v>3390</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Kai Fong</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -508,15 +512,11 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Kai Fong</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
         <v>0</v>
       </c>
@@ -707,7 +707,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>73.69</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -716,7 +716,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>39.38</v>
+        <v>45.15</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -741,7 +741,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -807,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>58.94</v>
+        <v>69</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,11 +452,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -465,20 +465,20 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3390</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -487,10 +487,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3390</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -500,37 +500,41 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chun Chieh</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -558,7 +562,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -571,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>157328</v>
+        <v>60056</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -580,7 +584,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -593,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>60056</v>
+        <v>157328</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -618,6 +622,24 @@
         <v>69621</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -707,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>80.93000000000001</v>
+        <v>95.34</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -716,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -732,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>45.15</v>
+        <v>50.73</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -741,7 +763,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -857,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>5.92</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -866,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,11 +538,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CRX</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
         <v>0</v>
       </c>
@@ -553,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>73394</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -562,7 +558,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -575,7 +571,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>60056</v>
+        <v>73394</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -606,38 +602,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>60056</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Chee</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>69621</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,7 +452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -465,7 +465,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3390</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -474,11 +474,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -487,10 +487,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3390</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -538,7 +538,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
@@ -549,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>73394</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -558,7 +562,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -571,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>73394</v>
+        <v>60056</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -602,7 +606,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Chee</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -615,18 +619,14 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>60056</v>
+        <v>69621</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Chee</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
         <v>0</v>
       </c>
@@ -637,7 +637,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>69621</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>69</v>
+        <v>79.25</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -468,7 +468,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>79.25</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,11 +538,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CRX</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
         <v>0</v>
       </c>
@@ -553,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>73394</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -562,7 +558,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -575,7 +571,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>60056</v>
+        <v>73394</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -606,38 +602,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>60056</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Chee</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>69621</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>95.34</v>
+        <v>102.8</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -571,7 +571,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>73394</v>
+        <v>76406</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>25078</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>102.8</v>
+        <v>110.18</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>5.92</v>
+        <v>22.36</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -571,7 +571,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>76406</v>
+        <v>96430</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>73394</v>
       </c>
       <c r="C2" t="n">
-        <v>7.66</v>
+        <v>26.35</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -637,7 +637,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>69621</v>
+        <v>122185</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69621</v>
+        <v>122185</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -571,7 +571,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>96430</v>
+        <v>239759</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73394</v>
+        <v>216723</v>
       </c>
       <c r="C2" t="n">
         <v>26.35</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,7 +538,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
@@ -549,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>239759</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -558,7 +562,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -571,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>239759</v>
+        <v>60056</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -593,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>157328</v>
+        <v>161532</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -602,7 +606,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Chee</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -615,18 +619,14 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>60056</v>
+        <v>122185</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Chee</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
         <v>0</v>
       </c>
@@ -637,7 +637,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>122185</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>157328</v>
+        <v>161532</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -468,7 +468,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>89.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -490,7 +490,7 @@
         <v>3390</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>110.18</v>
+        <v>117.23</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,11 +538,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CRX</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
         <v>0</v>
       </c>
@@ -553,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>239759</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -562,7 +558,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -575,7 +571,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>60056</v>
+        <v>195521</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -606,38 +602,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>60056</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Chee</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>122185</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>216723</v>
+        <v>172485</v>
       </c>
       <c r="C2" t="n">
         <v>26.35</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>25078</v>
+        <v>42210</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>22.36</v>
+        <v>33.71</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -468,7 +468,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -490,7 +490,7 @@
         <v>3390</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>117.23</v>
+        <v>120.87</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>50.73</v>
+        <v>56.3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -763,7 +763,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>99.90000000000001</v>
+        <v>110.26</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -468,7 +468,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -490,7 +490,7 @@
         <v>3390</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -538,7 +538,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CRX</t>
+        </is>
+      </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
@@ -549,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>195521</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -558,7 +562,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CRX</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -571,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>195521</v>
+        <v>60056</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -602,7 +606,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Chee</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -615,18 +619,14 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>60056</v>
+        <v>122185</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Chee</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
         <v>0</v>
       </c>
@@ -637,7 +637,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>122185</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>120.87</v>
+        <v>134.61</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>56.3</v>
+        <v>61.3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -763,7 +763,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>110.26</v>
+        <v>130.76</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/Strides_in_Sync_2026_Tally.xlsx
+++ b/Strides_in_Sync_2026_Tally.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -490,7 +490,7 @@
         <v>3390</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -538,11 +538,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CRX</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
         <v>0</v>
       </c>
@@ -553,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>195521</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -562,7 +558,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>CRX</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -575,7 +571,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>60056</v>
+        <v>195521</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -606,38 +602,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>60056</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Chee</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>122185</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>134.61</v>
+        <v>142.05</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
